--- a/Data/Home/BedroomTwo.UltravioletLevel.xlsx
+++ b/Data/Home/BedroomTwo.UltravioletLevel.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:I247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709259234</v>
+        <v>1711852895</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709259268</v>
+        <v>1711852909</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709259300</v>
+        <v>1711852926</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709259323</v>
+        <v>1711852943</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -593,10 +601,11 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709259358</v>
+        <v>1711860742</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709267547</v>
+        <v>1711872643</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -657,10 +667,11 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709272771</v>
+        <v>1711880128</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -689,10 +700,11 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709280273</v>
+        <v>1711880140</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -721,10 +733,11 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709281589</v>
+        <v>1711937846</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +770,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709282174</v>
+        <v>1711937879</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -785,10 +799,11 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709252580</v>
+        <v>1711938144</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -817,10 +832,11 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709252606</v>
+        <v>1711948730</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -849,10 +865,15 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +892,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709252634</v>
+        <v>1711954878</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +906,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +925,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709252662</v>
+        <v>1711964971</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -913,10 +935,11 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +958,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709252721</v>
+        <v>1711965265</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -945,10 +968,11 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +991,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709259407</v>
+        <v>1711965276</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +1001,11 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1024,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709263232</v>
+        <v>1712016902</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1009,10 +1034,11 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1057,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709269468</v>
+        <v>1712016924</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1071,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1090,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709270848</v>
+        <v>1712024685</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1073,10 +1100,11 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1123,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709270877</v>
+        <v>1712035135</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1105,10 +1133,15 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1160,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709338718</v>
+        <v>1712041504</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1137,10 +1170,11 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1193,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709338752</v>
+        <v>1712051264</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1207,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1226,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709343929</v>
+        <v>1712053210</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1201,10 +1236,11 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1259,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709352627</v>
+        <v>1712054058</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1233,10 +1269,11 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1292,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709359053</v>
+        <v>1712112831</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1306,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1325,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709360104</v>
+        <v>1712112844</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1297,10 +1335,11 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1358,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709425435</v>
+        <v>1712112860</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1329,10 +1368,11 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1391,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709425472</v>
+        <v>1712112879</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1361,10 +1401,15 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1428,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709429281</v>
+        <v>1712112911</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1442,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1461,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709438138</v>
+        <v>1712121189</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1425,10 +1471,15 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1498,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709444631</v>
+        <v>1712126364</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1457,10 +1508,11 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1531,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709445816</v>
+        <v>1712135300</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1489,10 +1541,11 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1564,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709511552</v>
+        <v>1712137149</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1578,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1597,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709511575</v>
+        <v>1712138005</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1553,10 +1607,11 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1630,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709511602</v>
+        <v>1712199712</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1585,10 +1640,11 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1663,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709511634</v>
+        <v>1712199727</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1617,10 +1673,11 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1696,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709511679</v>
+        <v>1712199742</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1710,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1729,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709518311</v>
+        <v>1712199756</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1743,11 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1766,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709523700</v>
+        <v>1712199798</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1780,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1799,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709532090</v>
+        <v>1712206993</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1745,10 +1809,15 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1836,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709532115</v>
+        <v>1712212385</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1777,10 +1846,11 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1869,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709532145</v>
+        <v>1712222005</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1809,10 +1879,11 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1902,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709598826</v>
+        <v>1712223220</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1916,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1935,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709598847</v>
+        <v>1712223230</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1873,10 +1945,11 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1968,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709598875</v>
+        <v>1712275746</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1905,10 +1978,11 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2001,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709598893</v>
+        <v>1712275764</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1937,10 +2011,11 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2034,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709598936</v>
+        <v>1712275777</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1969,10 +2044,11 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2067,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709605736</v>
+        <v>1712275790</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2001,10 +2077,11 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2100,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709611286</v>
+        <v>1712283574</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2033,10 +2110,11 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2133,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709619323</v>
+        <v>1712283586</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2147,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2166,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709621726</v>
+        <v>1712283600</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2097,10 +2176,11 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2199,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709622427</v>
+        <v>1712283616</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2129,10 +2209,15 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2236,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709680826</v>
+        <v>1712283650</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2161,10 +2246,11 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2269,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709680855</v>
+        <v>1712294392</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2193,10 +2279,15 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2306,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709684288</v>
+        <v>1712300228</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2320,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2339,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709693149</v>
+        <v>1712310078</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2257,10 +2349,11 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2372,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709697556</v>
+        <v>1712312327</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2289,10 +2382,11 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2405,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709705359</v>
+        <v>1712313293</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2321,10 +2415,11 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2438,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709706728</v>
+        <v>1712365714</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2452,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2471,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709707355</v>
+        <v>1712368828</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2385,10 +2481,11 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2504,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709767141</v>
+        <v>1712377546</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2417,10 +2514,11 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2537,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709767179</v>
+        <v>1712389018</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2551,7 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2570,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709769900</v>
+        <v>1712396465</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2481,10 +2580,11 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2603,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709777166</v>
+        <v>1712397855</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2513,10 +2613,11 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2636,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709781266</v>
+        <v>1712452313</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2545,10 +2646,11 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2669,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709788315</v>
+        <v>1712452333</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2683,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2702,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709789764</v>
+        <v>1712456463</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2609,10 +2712,11 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2735,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709790291</v>
+        <v>1712467778</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2641,10 +2745,15 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2772,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709850725</v>
+        <v>1712473272</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2673,10 +2782,11 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2805,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709850749</v>
+        <v>1712483159</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2819,7 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2838,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709855836</v>
+        <v>1712485175</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2737,10 +2848,11 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2871,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709863537</v>
+        <v>1712486222</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2769,10 +2881,11 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2904,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709867389</v>
+        <v>1712544393</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2801,10 +2914,11 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2937,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709874016</v>
+        <v>1712544418</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2951,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2970,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709875536</v>
+        <v>1712549396</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2865,10 +2980,11 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3003,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709876224</v>
+        <v>1712560415</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2897,10 +3013,11 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3036,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709944035</v>
+        <v>1712567831</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3050,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3069,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709944069</v>
+        <v>1712569182</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2961,10 +3079,11 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3102,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709944808</v>
+        <v>1712621684</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2993,10 +3112,11 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3135,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709953460</v>
+        <v>1712621702</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3025,10 +3145,11 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3168,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1709957432</v>
+        <v>1712630716</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3057,10 +3178,11 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3201,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1709965234</v>
+        <v>1712630732</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3215,7 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3234,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1709966931</v>
+        <v>1712630748</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3121,10 +3244,11 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3267,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1709966957</v>
+        <v>1712630761</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3153,10 +3277,15 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3304,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710031561</v>
+        <v>1712630797</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3185,10 +3314,11 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3337,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710031596</v>
+        <v>1712639831</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3217,10 +3347,15 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3374,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710031633</v>
+        <v>1712646382</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3388,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3407,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710031663</v>
+        <v>1712656383</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3281,10 +3417,11 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3440,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710031711</v>
+        <v>1712658130</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3313,10 +3450,11 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3473,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710036825</v>
+        <v>1712659053</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3345,10 +3483,11 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3506,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710041151</v>
+        <v>1712716159</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3377,10 +3516,11 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3539,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710048995</v>
+        <v>1712716180</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3553,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3572,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710050883</v>
+        <v>1712716191</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3441,10 +3582,11 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3605,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710051658</v>
+        <v>1712716205</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3473,10 +3615,15 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3642,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710117399</v>
+        <v>1712716240</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3505,10 +3652,11 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3675,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710117416</v>
+        <v>1712726305</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3537,10 +3685,15 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3712,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710117446</v>
+        <v>1712732314</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3726,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3745,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710117469</v>
+        <v>1712742219</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3601,10 +3755,11 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3778,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710117543</v>
+        <v>1712744264</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3633,10 +3788,11 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3811,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710123622</v>
+        <v>1712745064</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3665,10 +3821,11 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3844,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710128190</v>
+        <v>1712802586</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3697,10 +3854,11 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3877,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710136410</v>
+        <v>1712802603</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3891,7 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3910,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710137887</v>
+        <v>1712802624</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3761,10 +3920,11 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3943,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710138652</v>
+        <v>1712802637</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3793,10 +3953,15 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3980,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710206474</v>
+        <v>1712802682</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3825,10 +3990,11 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4013,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710206503</v>
+        <v>1712811452</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3857,10 +4023,15 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4050,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710212973</v>
+        <v>1712817571</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4064,7 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4083,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710222670</v>
+        <v>1712827147</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4097,7 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4116,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710228076</v>
+        <v>1712829397</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4130,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4149,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710228096</v>
+        <v>1712830470</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3989,6 +4163,7 @@
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4182,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710288282</v>
+        <v>1712889621</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4196,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4215,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710288313</v>
+        <v>1712889634</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4229,7 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4248,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710292464</v>
+        <v>1712889648</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4262,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4281,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710301676</v>
+        <v>1712897474</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4295,11 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4318,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710307668</v>
+        <v>1712903898</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4332,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4351,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710316202</v>
+        <v>1712914053</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4365,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4384,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710318751</v>
+        <v>1712916731</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4398,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4417,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710319355</v>
+        <v>1712917783</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4431,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4450,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710372941</v>
+        <v>1712970137</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4464,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4483,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710372975</v>
+        <v>1712972976</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4497,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4516,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710375391</v>
+        <v>1712981641</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4530,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4549,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710384240</v>
+        <v>1712993289</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4369,10 +4559,11 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4582,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710388395</v>
+        <v>1713000832</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4401,10 +4592,11 @@
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4615,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710395624</v>
+        <v>1713002244</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4433,10 +4625,11 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4648,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710398123</v>
+        <v>1713056755</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4662,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4681,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710398997</v>
+        <v>1713056774</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4497,10 +4691,11 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4714,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710464893</v>
+        <v>1713060446</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4529,10 +4724,11 @@
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4747,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710464926</v>
+        <v>1713069937</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4561,10 +4757,15 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4784,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710465065</v>
+        <v>1713075971</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4798,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4817,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710473105</v>
+        <v>1713086347</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4625,10 +4827,11 @@
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4850,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710478079</v>
+        <v>1713089149</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4657,10 +4860,11 @@
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4883,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710485186</v>
+        <v>1713090153</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4689,10 +4893,11 @@
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4916,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710486385</v>
+        <v>1713147637</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +4930,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4949,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710486945</v>
+        <v>1713147654</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4753,10 +4959,11 @@
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4982,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710548141</v>
+        <v>1713154111</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4785,10 +4992,11 @@
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +5015,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710548185</v>
+        <v>1713165427</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +5029,7 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5048,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710552137</v>
+        <v>1713172263</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4849,10 +5058,11 @@
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5081,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710559913</v>
+        <v>1713173809</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4881,10 +5091,11 @@
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5114,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710565231</v>
+        <v>1713236683</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5128,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5147,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710566306</v>
+        <v>1713236696</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4945,10 +5157,11 @@
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5180,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710635434</v>
+        <v>1713236710</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4977,10 +5190,11 @@
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5213,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710635469</v>
+        <v>1713236727</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5009,10 +5223,15 @@
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5250,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710635498</v>
+        <v>1713236769</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5264,7 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5283,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710635526</v>
+        <v>1713245385</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5077,6 +5297,11 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5320,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710635583</v>
+        <v>1713251899</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5109,6 +5334,7 @@
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5353,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710641999</v>
+        <v>1713261905</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5137,10 +5363,11 @@
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5386,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710646276</v>
+        <v>1713264965</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5169,10 +5396,11 @@
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5419,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710654023</v>
+        <v>1713265957</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5201,10 +5429,11 @@
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5452,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710655923</v>
+        <v>1713312154</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5237,6 +5466,7 @@
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5485,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710656701</v>
+        <v>1713312169</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5269,6 +5499,7 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5518,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710723091</v>
+        <v>1713322210</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5301,6 +5532,7 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5551,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710723118</v>
+        <v>1713322229</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5333,6 +5565,7 @@
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5584,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710723141</v>
+        <v>1713322248</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5365,6 +5598,7 @@
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5617,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710723162</v>
+        <v>1713322266</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5397,6 +5631,11 @@
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5654,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710723214</v>
+        <v>1713322296</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5429,6 +5668,7 @@
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5687,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710731777</v>
+        <v>1713331439</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5461,6 +5701,11 @@
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5724,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710737084</v>
+        <v>1713337497</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5493,6 +5738,7 @@
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5757,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710741902</v>
+        <v>1713346657</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5525,6 +5771,7 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5790,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710741925</v>
+        <v>1713348492</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5557,6 +5804,7 @@
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5823,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710741950</v>
+        <v>1713349336</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5589,6 +5837,7 @@
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5856,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710807868</v>
+        <v>1713406761</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5621,6 +5870,7 @@
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5889,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1710807898</v>
+        <v>1713406789</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5653,6 +5903,7 @@
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5922,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1710808253</v>
+        <v>1713413330</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5685,6 +5936,7 @@
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +5955,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1710817117</v>
+        <v>1713424589</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5713,10 +5965,11 @@
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +5988,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1710821922</v>
+        <v>1713432109</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5745,10 +5998,11 @@
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +6021,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1710829850</v>
+        <v>1713433498</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5777,10 +6031,11 @@
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +6054,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1710831684</v>
+        <v>1713485406</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +6068,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6087,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1710832375</v>
+        <v>1713485426</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5841,10 +6097,11 @@
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6120,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1710888186</v>
+        <v>1713492905</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5873,10 +6130,11 @@
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6153,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1710888219</v>
+        <v>1713502732</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5905,10 +6163,15 @@
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6190,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1710888245</v>
+        <v>1713509023</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5941,6 +6204,7 @@
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6223,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1710888292</v>
+        <v>1713518497</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5973,6 +6237,7 @@
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6256,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1710892283</v>
+        <v>1713521204</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6001,10 +6266,11 @@
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6289,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1710901326</v>
+        <v>1713521977</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6033,10 +6299,11 @@
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6322,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1710906121</v>
+        <v>1713575233</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6065,10 +6332,11 @@
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6355,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1710914782</v>
+        <v>1713575254</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6101,6 +6369,7 @@
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6388,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1710917278</v>
+        <v>1713580879</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6129,10 +6398,11 @@
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6421,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1710917932</v>
+        <v>1713592323</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6161,10 +6431,15 @@
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6458,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1710976906</v>
+        <v>1713597674</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6193,10 +6468,11 @@
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6491,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1710976945</v>
+        <v>1713607964</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6229,6 +6505,7 @@
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6247,7 +6524,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1710980186</v>
+        <v>1713610786</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6257,10 +6534,11 @@
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6279,7 +6557,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1710989517</v>
+        <v>1713611773</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6289,10 +6567,11 @@
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6311,7 +6590,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1710993942</v>
+        <v>1713661277</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6321,10 +6600,11 @@
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6343,7 +6623,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1711001328</v>
+        <v>1713661296</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6357,6 +6637,7 @@
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6375,7 +6656,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1711002963</v>
+        <v>1713664410</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6385,10 +6666,11 @@
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6407,7 +6689,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1711003782</v>
+        <v>1713673852</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6417,10 +6699,15 @@
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6439,7 +6726,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1711067747</v>
+        <v>1713679623</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6449,10 +6736,11 @@
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,7 +6759,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1711067776</v>
+        <v>1713689069</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6485,6 +6773,7 @@
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6503,7 +6792,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1711067808</v>
+        <v>1713690993</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6513,10 +6802,11 @@
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6535,7 +6825,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1711067842</v>
+        <v>1713691803</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6545,10 +6835,11 @@
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6567,7 +6858,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1711067935</v>
+        <v>1713752024</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6577,10 +6868,11 @@
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6599,7 +6891,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1711074714</v>
+        <v>1713752036</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6609,10 +6901,11 @@
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6631,7 +6924,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1711079504</v>
+        <v>1713752056</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6645,6 +6938,7 @@
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6663,7 +6957,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1711086902</v>
+        <v>1713752075</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6673,10 +6967,15 @@
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6695,7 +6994,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1711088675</v>
+        <v>1713752121</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6705,10 +7004,11 @@
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6727,7 +7027,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1711089226</v>
+        <v>1713760847</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6737,10 +7037,15 @@
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6759,7 +7064,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1711153741</v>
+        <v>1713767351</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6769,10 +7074,11 @@
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6791,7 +7097,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1711153764</v>
+        <v>1713776696</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6805,6 +7111,7 @@
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6823,7 +7130,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1711153797</v>
+        <v>1713778411</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6833,10 +7140,11 @@
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6855,7 +7163,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1711153817</v>
+        <v>1713779190</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6865,10 +7173,11 @@
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6887,7 +7196,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1711153884</v>
+        <v>1713830453</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6897,10 +7206,11 @@
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6919,7 +7229,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1711162051</v>
+        <v>1713830484</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6929,10 +7239,11 @@
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6951,7 +7262,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1711166742</v>
+        <v>1713837795</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6965,6 +7276,7 @@
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6983,7 +7295,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1711173842</v>
+        <v>1713848154</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6993,10 +7305,15 @@
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7015,7 +7332,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1711175496</v>
+        <v>1713854580</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7025,10 +7342,11 @@
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7047,7 +7365,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1711175529</v>
+        <v>1713863627</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7057,10 +7375,11 @@
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7079,7 +7398,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1711242934</v>
+        <v>1713866033</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7093,6 +7412,7 @@
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7111,7 +7431,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1711242962</v>
+        <v>1713866890</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7121,10 +7441,11 @@
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7143,7 +7464,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1711242987</v>
+        <v>1713926232</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7153,10 +7474,11 @@
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7175,7 +7497,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1711243019</v>
+        <v>1713926256</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7185,10 +7507,11 @@
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7207,7 +7530,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1711243075</v>
+        <v>1713931436</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -7221,6 +7544,7 @@
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7239,7 +7563,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1711251114</v>
+        <v>1713943084</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -7249,10 +7573,11 @@
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7271,7 +7596,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1711256830</v>
+        <v>1713950566</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -7281,10 +7606,11 @@
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7303,7 +7629,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1711265329</v>
+        <v>1713952008</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -7313,10 +7639,11 @@
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7335,7 +7662,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1711267728</v>
+        <v>1714013005</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -7349,6 +7676,7 @@
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7367,7 +7695,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1711268440</v>
+        <v>1714013030</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -7377,10 +7705,11 @@
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7399,7 +7728,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1711330598</v>
+        <v>1714018072</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -7409,10 +7738,11 @@
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7431,7 +7761,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1711330622</v>
+        <v>1714028999</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -7445,6 +7775,7 @@
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7463,7 +7794,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1711330648</v>
+        <v>1714036201</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -7473,10 +7804,11 @@
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7495,7 +7827,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1711330677</v>
+        <v>1714037562</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -7505,10 +7837,11 @@
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7527,7 +7860,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1711330738</v>
+        <v>1714098942</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7537,10 +7870,11 @@
       <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7559,7 +7893,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1711336211</v>
+        <v>1714098956</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7569,10 +7903,11 @@
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7591,7 +7926,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1711341920</v>
+        <v>1714098970</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7605,6 +7940,7 @@
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7623,7 +7959,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1711350497</v>
+        <v>1714098983</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7633,10 +7969,15 @@
       <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7655,7 +7996,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1711352463</v>
+        <v>1714099024</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7665,10 +8006,11 @@
       <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7687,7 +8029,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1711353218</v>
+        <v>1714108960</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7697,10 +8039,15 @@
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7719,7 +8066,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1711422027</v>
+        <v>1714115448</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7729,10 +8076,11 @@
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7751,7 +8099,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1711422041</v>
+        <v>1714125436</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7765,6 +8113,7 @@
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7783,7 +8132,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1711422055</v>
+        <v>1714127549</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7793,10 +8142,11 @@
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7815,7 +8165,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1711422069</v>
+        <v>1714128517</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7825,10 +8175,11 @@
       <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7847,7 +8198,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1711422104</v>
+        <v>1714179901</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7857,10 +8208,11 @@
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7879,7 +8231,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1711431057</v>
+        <v>1714179920</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7889,10 +8241,11 @@
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7911,7 +8264,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1711437915</v>
+        <v>1714184084</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7925,6 +8278,7 @@
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7943,7 +8297,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1711448443</v>
+        <v>1714194913</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7953,10 +8307,15 @@
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7975,7 +8334,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1711451298</v>
+        <v>1714201430</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7985,10 +8344,11 @@
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8007,7 +8367,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1711452139</v>
+        <v>1714211600</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -8017,10 +8377,11 @@
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8039,7 +8400,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1711502273</v>
+        <v>1714213985</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -8053,6 +8414,7 @@
         </is>
       </c>
       <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8071,7 +8433,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1711502288</v>
+        <v>1714214903</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -8081,10 +8443,11 @@
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8103,7 +8466,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1711507005</v>
+        <v>1714267211</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -8113,10 +8476,11 @@
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8135,7 +8499,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1711518870</v>
+        <v>1714267225</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -8145,10 +8509,11 @@
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8167,7 +8532,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1711526208</v>
+        <v>1714271981</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -8181,6 +8546,7 @@
         </is>
       </c>
       <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8199,7 +8565,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1711536764</v>
+        <v>1714282437</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -8209,10 +8575,15 @@
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8231,7 +8602,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1711538965</v>
+        <v>1714287886</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -8241,10 +8612,11 @@
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8263,7 +8635,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1711539850</v>
+        <v>1714298204</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -8273,10 +8645,11 @@
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8295,7 +8668,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1711588728</v>
+        <v>1714300868</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -8309,6 +8682,7 @@
         </is>
       </c>
       <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8327,7 +8701,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1711588752</v>
+        <v>1714301998</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -8337,202 +8711,11 @@
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr">
         <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
+          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D248" t="n">
-        <v>1711592390</v>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr"/>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr"/>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D249" t="n">
-        <v>1711604060</v>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyHigh</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr"/>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D250" t="n">
-        <v>1711610628</v>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr"/>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D251" t="n">
-        <v>1711621225</v>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>BedroomTwo.UltravioletLevel.state: Moderate</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr"/>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D252" t="n">
-        <v>1711623820</v>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>BedroomTwo.UltravioletLevel.state: RelativelyLow</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr"/>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>BedroomTwo</t>
-        </is>
-      </c>
-      <c r="D253" t="n">
-        <v>1711624716</v>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>BedroomTwo.UltravioletLevel.state: ExcessivelyLow</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
